--- a/thesis/stats.xlsx
+++ b/thesis/stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boti\Desktop\Mernokinfo\szakdoga\Position-Based-Fluids-Thesis\thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mernokinfo\szakdoga\Position-Based-Fluids-Thesis\thesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFF7490-2CB6-4409-80DE-0138470AC29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3514128-02A2-4413-8B14-42199A215263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -122,9 +122,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>FPS vs particle count</a:t>
+              <a:rPr lang="hu-HU"/>
+              <a:t>RTX</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU" baseline="0"/>
+              <a:t> 3080</a:t>
+            </a:r>
+            <a:endParaRPr lang="hu-HU"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -153,7 +158,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="hu-HU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -161,7 +166,7 @@
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -225,41 +230,41 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$C$2:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>115</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>48</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>17</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C099-4E3D-B95E-5FD25B92C511}"/>
+              <c16:uniqueId val="{00000000-F2B0-45ED-B884-D9973CEDAFC2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -271,11 +276,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1301351584"/>
-        <c:axId val="1301355904"/>
+        <c:axId val="842583072"/>
+        <c:axId val="842582712"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1301351584"/>
+        <c:axId val="842583072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -295,6 +300,96 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="hu-HU" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>particle count (thousand)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="hu-HU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -329,15 +424,15 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="hu-HU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301355904"/>
+        <c:crossAx val="842582712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1301355904"/>
+        <c:axId val="842582712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -357,6 +452,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="hu-HU"/>
+                  <a:t>FPS</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="hu-HU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -391,10 +541,10 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="hu-HU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301351584"/>
+        <c:crossAx val="842583072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -439,7 +589,1048 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>RTX</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU" baseline="0"/>
+              <a:t> 4050 Laptop</a:t>
+            </a:r>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-66DB-47BD-A15C-56F08B60F349}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="741857184"/>
+        <c:axId val="741849624"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="741857184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="hu-HU"/>
+                  <a:t>particle</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="hu-HU" baseline="0"/>
+                  <a:t> count (thousand)</a:t>
+                </a:r>
+                <a:endParaRPr lang="hu-HU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="hu-HU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741849624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="741849624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="hu-HU"/>
+                  <a:t>FPS</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="hu-HU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="741857184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>RTX 4050 Laptop</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1DC8-4110-9962-83516D86EEE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>RTX 3080</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1DC8-4110-9962-83516D86EEE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="932422704"/>
+        <c:axId val="970766936"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="932422704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="hu-HU"/>
+                  <a:t>particle count</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="hu-HU" baseline="0"/>
+                  <a:t> (thousand)</a:t>
+                </a:r>
+                <a:endParaRPr lang="hu-HU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="hu-HU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="970766936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="970766936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="hu-HU"/>
+                  <a:t>FPS</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="hu-HU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="932422704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -490,6 +1681,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1006,27 +2277,1059 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Diagram 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A579D905-9486-2764-1F47-5922703E1F7F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05186F0D-BE7C-28E2-3CB6-A40CF8A08280}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1039,6 +3342,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>23811</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Diagram 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FED66B1-D715-9554-8046-E5259C845C43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>347662</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57CA687A-2C48-5F29-3D92-ED259A2090EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1311,12 +3686,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1327,68 +3702,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>100</v>
       </c>
       <c r="B2">
         <v>115</v>
       </c>
+      <c r="C2">
+        <v>144</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>200</v>
       </c>
       <c r="B3">
         <v>73</v>
       </c>
+      <c r="C3">
+        <v>140</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>300</v>
       </c>
       <c r="B4">
         <v>48</v>
       </c>
+      <c r="C4">
+        <v>105</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>400</v>
       </c>
       <c r="B5">
         <v>39</v>
       </c>
+      <c r="C5">
+        <v>80</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>500</v>
       </c>
       <c r="B6">
         <v>32</v>
       </c>
+      <c r="C6">
+        <v>65</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>600</v>
       </c>
       <c r="B7">
         <v>26</v>
       </c>
+      <c r="C7">
+        <v>55</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>700</v>
       </c>
       <c r="B8">
         <v>20</v>
       </c>
+      <c r="C8">
+        <v>48</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>800</v>
       </c>
       <c r="B9">
         <v>17</v>
+      </c>
+      <c r="C9">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
